--- a/Backend/utils/data/Okere City Mothers.xlsx
+++ b/Backend/utils/data/Okere City Mothers.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Documents/CARIYA/cariya_wallet/Backend/utils/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFF5D085-FF5E-694D-9535-353F83EFF5BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24C2FE14-511B-E448-AD24-3180F39FADB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15980" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="33">
   <si>
     <t>How to use guide for the sheet as follows;</t>
   </si>
@@ -235,9 +235,6 @@
   </si>
   <si>
     <t>Education Level</t>
-  </si>
-  <si>
-    <t>Bottle Recycling</t>
   </si>
 </sst>
 </file>
@@ -30732,7 +30729,7 @@
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B2" s="21">
         <v>782781759</v>
